--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO TOLEDO BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLUB BALONCESTO TOLEDO BASKET.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>85.35119999999999</v>
+        <v>76.1221</v>
       </c>
       <c r="E2" t="n">
-        <v>41.5389</v>
+        <v>36.8336</v>
       </c>
       <c r="F2" t="n">
-        <v>43.812</v>
+        <v>39.2885</v>
       </c>
       <c r="G2" t="n">
         <v>58.5486</v>
@@ -610,13 +610,13 @@
         <v>53.9027</v>
       </c>
       <c r="S2" t="n">
-        <v>21.5517</v>
+        <v>12.3229</v>
       </c>
       <c r="T2" t="n">
-        <v>6.7433</v>
+        <v>2.038</v>
       </c>
       <c r="U2" t="n">
-        <v>14.8084</v>
+        <v>10.2847</v>
       </c>
       <c r="V2" t="n">
         <v>0.6721999999999996</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>50.3612</v>
+        <v>41.3347</v>
       </c>
       <c r="E3" t="n">
-        <v>30.4949</v>
+        <v>28.1558</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8663</v>
+        <v>13.1791</v>
       </c>
       <c r="G3" t="n">
-        <v>19.2368</v>
+        <v>25.8924</v>
       </c>
       <c r="H3" t="n">
-        <v>15.2141</v>
+        <v>13.063</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0229</v>
+        <v>12.8294</v>
       </c>
       <c r="J3" t="n">
-        <v>27.5975</v>
+        <v>30.251</v>
       </c>
       <c r="K3" t="n">
-        <v>15.4759</v>
+        <v>13.6094</v>
       </c>
       <c r="L3" t="n">
-        <v>12.1217</v>
+        <v>16.6417</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.3606</v>
+        <v>-4.358599999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2619000000000002</v>
+        <v>-0.5462000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.098699999999999</v>
+        <v>-3.8123</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.664999999999999</v>
+        <v>7.0759</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34.3395</v>
+        <v>-18.7307</v>
       </c>
       <c r="R3" t="n">
-        <v>32.6747</v>
+        <v>25.8064</v>
       </c>
       <c r="S3" t="n">
-        <v>17.4485</v>
+        <v>7.7685</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7146</v>
+        <v>2.2184</v>
       </c>
       <c r="U3" t="n">
-        <v>13.734</v>
+        <v>5.5504</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3405</v>
+        <v>0.5979000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>33.5221</v>
+        <v>14.4173</v>
       </c>
       <c r="X3" t="n">
-        <v>-18.1817</v>
+        <v>-13.8193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>43.4125</v>
+        <v>39.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>31.1885</v>
+        <v>26.0688</v>
       </c>
       <c r="F4" t="n">
-        <v>12.224</v>
+        <v>13.3816</v>
       </c>
       <c r="G4" t="n">
-        <v>25.8924</v>
+        <v>19.2368</v>
       </c>
       <c r="H4" t="n">
-        <v>13.063</v>
+        <v>15.2141</v>
       </c>
       <c r="I4" t="n">
-        <v>12.8294</v>
+        <v>4.0229</v>
       </c>
       <c r="J4" t="n">
-        <v>30.251</v>
+        <v>27.5975</v>
       </c>
       <c r="K4" t="n">
-        <v>13.6094</v>
+        <v>15.4759</v>
       </c>
       <c r="L4" t="n">
-        <v>16.6417</v>
+        <v>12.1217</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.358599999999999</v>
+        <v>-8.3606</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5462000000000001</v>
+        <v>-0.2619000000000002</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.8123</v>
+        <v>-8.098699999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>7.0759</v>
+        <v>-1.664999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-18.7307</v>
+        <v>-34.3395</v>
       </c>
       <c r="R4" t="n">
-        <v>25.8064</v>
+        <v>32.6747</v>
       </c>
       <c r="S4" t="n">
-        <v>9.8462</v>
+        <v>6.5378</v>
       </c>
       <c r="T4" t="n">
-        <v>5.250999999999999</v>
+        <v>-0.7109000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5953</v>
+        <v>7.2492</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5979000000000001</v>
+        <v>15.3405</v>
       </c>
       <c r="W4" t="n">
-        <v>14.4173</v>
+        <v>33.5221</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.8193</v>
+        <v>-18.1817</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>28.2229</v>
+        <v>36.3873</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1172</v>
+        <v>5.942600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>26.1053</v>
+        <v>30.4448</v>
       </c>
       <c r="G5" t="n">
         <v>22.3283</v>
@@ -844,13 +844,13 @@
         <v>51.6131</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.8871</v>
+        <v>2.2773</v>
       </c>
       <c r="T5" t="n">
-        <v>-6.5092</v>
+        <v>-2.6842</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6224000000000001</v>
+        <v>4.9617</v>
       </c>
       <c r="V5" t="n">
         <v>15.3197</v>
@@ -877,13 +877,13 @@
         <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>19.1832</v>
+        <v>20.0382</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8034</v>
+        <v>12.6231</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3795</v>
+        <v>7.4152</v>
       </c>
       <c r="G6" t="n">
         <v>12.3543</v>
@@ -922,13 +922,13 @@
         <v>24.7661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9856000000000003</v>
+        <v>1.841</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9341</v>
+        <v>0.7539999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.9485</v>
+        <v>1.0868</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8574</v>
@@ -955,13 +955,13 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9446</v>
+        <v>4.330399999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-11.2125</v>
+        <v>-9.9871</v>
       </c>
       <c r="F7" t="n">
-        <v>13.1568</v>
+        <v>14.3175</v>
       </c>
       <c r="G7" t="n">
         <v>4.110300000000001</v>
@@ -1000,13 +1000,13 @@
         <v>23.9335</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.954</v>
+        <v>0.4321999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.8582</v>
+        <v>-1.6329</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9045000000000001</v>
+        <v>2.065</v>
       </c>
       <c r="V7" t="n">
         <v>2.2856</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HERNANDEZ RODRIGUEZ</t>
+          <t>G. VILLAREJO COSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2859</v>
+        <v>1.761000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3551</v>
+        <v>-1.7645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06909999999999994</v>
+        <v>3.5255</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5778</v>
+        <v>-1.192</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5459</v>
+        <v>3.4468</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03179999999999994</v>
+        <v>-4.6389</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7777000000000001</v>
+        <v>1.0421</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0642</v>
+        <v>6.7749</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2865999999999999</v>
+        <v>-5.7331</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8004</v>
+        <v>-2.2343</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4818</v>
+        <v>-3.3285</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3185</v>
+        <v>1.0941</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>-1.0408</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-9.781599999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>8.7408</v>
       </c>
       <c r="S8" t="n">
-        <v>0.719</v>
+        <v>-1.3379</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7764000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.05760000000000001</v>
+        <v>-0.5117</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6758000000000001</v>
+        <v>5.331899999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3538</v>
+        <v>7.8014</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.322</v>
+        <v>-2.4695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. VILLAREJO COSTA</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7580999999999994</v>
+        <v>1.615599999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3656</v>
+        <v>-4.717000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6073</v>
+        <v>6.3321</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.192</v>
+        <v>4.057199999999998</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4468</v>
+        <v>2.8131</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.6389</v>
+        <v>1.244100000000002</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0421</v>
+        <v>20.1465</v>
       </c>
       <c r="K9" t="n">
-        <v>6.7749</v>
+        <v>11.6366</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.7331</v>
+        <v>8.5101</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2343</v>
+        <v>-16.0893</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.3285</v>
+        <v>-8.823399999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0941</v>
+        <v>-7.266</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0408</v>
+        <v>-2.4972</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.781599999999999</v>
+        <v>-47.4512</v>
       </c>
       <c r="R9" t="n">
-        <v>8.7408</v>
+        <v>44.9535</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.8568</v>
+        <v>-4.5509</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.427</v>
+        <v>-3.8413</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.43</v>
+        <v>-0.7095999999999997</v>
       </c>
       <c r="V9" t="n">
-        <v>5.331899999999999</v>
+        <v>4.6065</v>
       </c>
       <c r="W9" t="n">
-        <v>7.8014</v>
+        <v>26.4285</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4695</v>
+        <v>-21.8222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>M. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.8269</v>
+        <v>-0.7821</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.474499999999999</v>
+        <v>-0.998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3527</v>
+        <v>0.2159</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04719999999999958</v>
+        <v>-1.5778</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9712000000000008</v>
+        <v>-1.5459</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9233000000000002</v>
+        <v>-0.03179999999999994</v>
       </c>
       <c r="J10" t="n">
-        <v>13.4029</v>
+        <v>-0.7777000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>7.8136</v>
+        <v>-1.0642</v>
       </c>
       <c r="L10" t="n">
-        <v>5.5893</v>
+        <v>0.2865999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-13.4501</v>
+        <v>-0.8004</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.784699999999999</v>
+        <v>-0.4818</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.6659</v>
+        <v>-0.3185</v>
       </c>
       <c r="P10" t="n">
-        <v>-17.0656</v>
+        <v>1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-47.2432</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>30.1772</v>
+        <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3544</v>
+        <v>0.2228</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8099</v>
+        <v>0.1334</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5445000000000002</v>
+        <v>0.08939999999999997</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9318</v>
+        <v>-0.6758000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>20.5553</v>
+        <v>-0.3538</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.6239</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.1035</v>
+        <v>-8.591100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.8959</v>
+        <v>-4.6755</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7923</v>
+        <v>-3.9155</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0113</v>
+        <v>7.5055</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4542</v>
+        <v>9.2134</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.4655</v>
+        <v>-1.7081</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1858</v>
+        <v>20.7065</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9087</v>
+        <v>13.369</v>
       </c>
       <c r="L11" t="n">
-        <v>-10.0942</v>
+        <v>7.337699999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8258</v>
+        <v>-13.2013</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4546</v>
+        <v>-4.1554</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6285999999999998</v>
+        <v>-9.0457</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.202999999999999</v>
+        <v>-9.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-14.1521</v>
+        <v>-38.7101</v>
       </c>
       <c r="R11" t="n">
-        <v>8.9491</v>
+        <v>28.9284</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4177000000000003</v>
+        <v>-1.2063</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0231</v>
+        <v>-0.3992</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6057</v>
+        <v>-0.8067</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5283</v>
+        <v>-5.108599999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>7.465</v>
+        <v>13.7274</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.9366</v>
+        <v>-18.836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.8729</v>
+        <v>-8.8193</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.3877</v>
+        <v>-11.9796</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4853</v>
+        <v>3.160200000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>4.057199999999998</v>
+        <v>-6.0113</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8131</v>
+        <v>3.4542</v>
       </c>
       <c r="I12" t="n">
-        <v>1.244100000000002</v>
+        <v>-9.4655</v>
       </c>
       <c r="J12" t="n">
-        <v>20.1465</v>
+        <v>-4.1858</v>
       </c>
       <c r="K12" t="n">
-        <v>11.6366</v>
+        <v>5.9087</v>
       </c>
       <c r="L12" t="n">
-        <v>8.5101</v>
+        <v>-10.0942</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.0893</v>
+        <v>-1.8258</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.823399999999999</v>
+        <v>-2.4546</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.266</v>
+        <v>0.6285999999999998</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4972</v>
+        <v>-5.202999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-47.4512</v>
+        <v>-14.1521</v>
       </c>
       <c r="R12" t="n">
-        <v>44.9535</v>
+        <v>8.9491</v>
       </c>
       <c r="S12" t="n">
-        <v>-21.0388</v>
+        <v>0.8665999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-12.5118</v>
+        <v>-1.107</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.527200000000001</v>
+        <v>1.9737</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6065</v>
+        <v>1.5283</v>
       </c>
       <c r="W12" t="n">
-        <v>26.4285</v>
+        <v>7.465</v>
       </c>
       <c r="X12" t="n">
-        <v>-21.8222</v>
+        <v>-5.9366</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.1198</v>
+        <v>-12.5035</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.6577</v>
+        <v>-11.7498</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.4621</v>
+        <v>-0.7534000000000005</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5055</v>
+        <v>-0.04719999999999958</v>
       </c>
       <c r="H13" t="n">
-        <v>9.2134</v>
+        <v>-0.9712000000000008</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7081</v>
+        <v>0.9233000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>20.7065</v>
+        <v>13.4029</v>
       </c>
       <c r="K13" t="n">
-        <v>13.369</v>
+        <v>7.8136</v>
       </c>
       <c r="L13" t="n">
-        <v>7.337699999999999</v>
+        <v>5.5893</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.2013</v>
+        <v>-13.4501</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.1554</v>
+        <v>-8.784699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.0457</v>
+        <v>-4.6659</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.7814</v>
+        <v>-17.0656</v>
       </c>
       <c r="Q13" t="n">
-        <v>-38.7101</v>
+        <v>-47.2432</v>
       </c>
       <c r="R13" t="n">
-        <v>28.9284</v>
+        <v>30.1772</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.735</v>
+        <v>2.6782</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.3815</v>
+        <v>1.5348</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.3532</v>
+        <v>1.1433</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.108599999999999</v>
+        <v>1.9318</v>
       </c>
       <c r="W13" t="n">
-        <v>13.7274</v>
+        <v>20.5553</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.836</v>
+        <v>-18.6239</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-65.2756</v>
+        <v>-54.63939999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-39.5623</v>
+        <v>-36.194</v>
       </c>
       <c r="F14" t="n">
-        <v>-25.7129</v>
+        <v>-18.4455</v>
       </c>
       <c r="G14" t="n">
         <v>-25.1855</v>
@@ -1546,13 +1546,13 @@
         <v>27.4717</v>
       </c>
       <c r="S14" t="n">
-        <v>-16.0252</v>
+        <v>-5.3895</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4024</v>
+        <v>-1.0341</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.6227</v>
+        <v>-4.355300000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-23.8566</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>108.2329</v>
+        <v>135.7047</v>
       </c>
       <c r="E15" t="n">
-        <v>22.2316</v>
+        <v>27.55839999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>85.9996</v>
+        <v>108.146</v>
       </c>
       <c r="G15" t="n">
         <v>120.0196</v>
@@ -1603,7 +1603,7 @@
         <v>152.0317</v>
       </c>
       <c r="L15" t="n">
-        <v>86.0894</v>
+        <v>86.08939999999998</v>
       </c>
       <c r="M15" t="n">
         <v>-118.1019</v>
@@ -1615,7 +1615,7 @@
         <v>-61.57579999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-22.89279999999999</v>
+        <v>-22.8928</v>
       </c>
       <c r="Q15" t="n">
         <v>-386.0611</v>
@@ -1624,13 +1624,13 @@
         <v>363.1659</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.009200000000011</v>
+        <v>22.4627</v>
       </c>
       <c r="T15" t="n">
-        <v>-10.8839</v>
+        <v>-5.5571</v>
       </c>
       <c r="U15" t="n">
-        <v>5.875599999999997</v>
+        <v>28.0209</v>
       </c>
       <c r="V15" t="n">
         <v>16.11600000000001</v>
